--- a/artfynd/A 33882-2024 artfynd.xlsx
+++ b/artfynd/A 33882-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ19"/>
+  <dimension ref="A1:AZ22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>102713332</v>
+        <v>136872860</v>
       </c>
       <c r="B2" t="n">
-        <v>80433</v>
+        <v>79555</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,40 +691,44 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>864</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Öretjärnsbäcken, Dlr</t>
+          <t>Kerstibygget, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>361421</v>
+        <v>363248</v>
       </c>
       <c r="R2" t="n">
-        <v>6882867</v>
+        <v>6883112</v>
       </c>
       <c r="S2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,27 +752,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-08-06</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-08-06</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:55</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Sälgen står i kanten av ett hygge.</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,13 +793,13 @@
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102713332</t>
+          <t>https://artportalen.se/Sighting/136872860</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119352037</v>
+        <v>102713332</v>
       </c>
       <c r="B3" t="n">
         <v>80433</v>
@@ -834,17 +833,17 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Öretjärnbäcken, Dlr</t>
+          <t>Öretjärnsbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>362300</v>
+        <v>361421</v>
       </c>
       <c r="R3" t="n">
-        <v>6883157</v>
+        <v>6882867</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -868,17 +867,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-08-25</t>
+          <t>2022-08-06</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-08-25</t>
+          <t>2022-08-06</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På gammal sälg.</t>
+          <t>Sälgen står i kanten av ett hygge.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,34 +896,33 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Carl Wiking</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Carl Wiking</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119352037</t>
+          <t>https://artportalen.se/Sighting/102713332</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121206393</v>
+        <v>119352037</v>
       </c>
       <c r="B4" t="n">
-        <v>91831</v>
+        <v>80433</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -922,37 +930,40 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3242</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kerstibygget, Kerstibygget, Dlr</t>
+          <t>Öretjärnbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>363237</v>
+        <v>362300</v>
       </c>
       <c r="R4" t="n">
-        <v>6883017</v>
+        <v>6883157</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -976,22 +987,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>11:32</t>
+          <t>2024-08-25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>11:32</t>
+          <t>2024-08-25</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På gammal sälg.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1000,98 +1006,72 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Dead branch  # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Carl Wiking</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Carl Wiking</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121206393</t>
+          <t>https://artportalen.se/Sighting/119352037</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>114387775</v>
+        <v>121206393</v>
       </c>
       <c r="B5" t="n">
-        <v>79327</v>
+        <v>91831</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>3242</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kokällmyren, Dlr</t>
+          <t>Kerstibygget, Kerstibygget, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>362379</v>
+        <v>363237</v>
       </c>
       <c r="R5" t="n">
-        <v>6883037</v>
+        <v>6883017</v>
       </c>
       <c r="S5" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1115,27 +1095,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-01-25</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-01-25</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:33</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Granar draperade med garnlav</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1146,76 +1121,96 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Dead branch  # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/114387775</t>
+          <t>https://artportalen.se/Sighting/121206393</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120682160</v>
+        <v>136872944</v>
       </c>
       <c r="B6" t="n">
-        <v>79327</v>
+        <v>92035</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>3242</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Västerkölen, Dlr</t>
+          <t>Kerstibygget, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>362634</v>
+        <v>363247</v>
       </c>
       <c r="R6" t="n">
-        <v>6882998</v>
+        <v>6883111</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1239,27 +1234,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:29</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Draperade granar i naturskog. Garnlav med apothecier</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1285,13 +1275,13 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120682160</t>
+          <t>https://artportalen.se/Sighting/136872944</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128821017</v>
+        <v>114387775</v>
       </c>
       <c r="B7" t="n">
         <v>79327</v>
@@ -1333,13 +1323,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>361967</v>
+        <v>362379</v>
       </c>
       <c r="R7" t="n">
-        <v>6883096</v>
+        <v>6883037</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1363,22 +1353,27 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2024-01-25</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2024-01-25</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>15:33</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Granar draperade med garnlav</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1404,13 +1399,13 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128821017</t>
+          <t>https://artportalen.se/Sighting/114387775</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128821031</v>
+        <v>120682160</v>
       </c>
       <c r="B8" t="n">
         <v>79327</v>
@@ -1439,23 +1434,23 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kokällmyren, Dlr</t>
+          <t>Västerkölen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>361972</v>
+        <v>362634</v>
       </c>
       <c r="R8" t="n">
-        <v>6883098</v>
+        <v>6882998</v>
       </c>
       <c r="S8" t="n">
         <v>4</v>
@@ -1482,22 +1477,27 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Draperade granar i naturskog. Garnlav med apothecier</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1523,16 +1523,16 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128821031</t>
+          <t>https://artportalen.se/Sighting/120682160</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121898927</v>
+        <v>128821017</v>
       </c>
       <c r="B9" t="n">
-        <v>83305</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1540,37 +1540,44 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6486</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kerstibygget, Kerstibygget, Dlr</t>
+          <t>Kokällmyren, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>363129</v>
+        <v>361967</v>
       </c>
       <c r="R9" t="n">
-        <v>6882975</v>
+        <v>6883096</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1594,22 +1601,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-01-04</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-01-04</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1624,73 +1631,72 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Andreas Öster, Maria Hindemo, Cecilia Öster</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121898927</t>
+          <t>https://artportalen.se/Sighting/128821017</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>82113833</v>
+        <v>128821031</v>
       </c>
       <c r="B10" t="n">
-        <v>57953</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Grövelsjön, Lövåsen, drygt 1 km VNV Lövåsen utefter skidspåret, Dlr</t>
+          <t>Kokällmyren, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>362381</v>
+        <v>361972</v>
       </c>
       <c r="R10" t="n">
-        <v>6883040</v>
+        <v>6883098</v>
       </c>
       <c r="S10" t="n">
-        <v>100</v>
+        <v>4</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1714,17 +1720,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2020-02-09</t>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2020-02-09</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Hackspår på tall o gran</t>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1735,91 +1746,80 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Fjällblandskog</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>Äldre fjällnära skog; mycket småmyrar</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Mats Lindqvist</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Mats Lindqvist</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/82113833</t>
+          <t>https://artportalen.se/Sighting/128821031</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>114387742</v>
+        <v>136873109</v>
       </c>
       <c r="B11" t="n">
-        <v>57953</v>
+        <v>79476</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Kokällmyren, Dlr</t>
+          <t>Kerstibygget, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>362387</v>
+        <v>363276</v>
       </c>
       <c r="R11" t="n">
-        <v>6883024</v>
+        <v>6883022</v>
       </c>
       <c r="S11" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1843,22 +1843,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-01-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-01-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1884,58 +1884,54 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/114387742</t>
+          <t>https://artportalen.se/Sighting/136873109</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119352008</v>
+        <v>121898927</v>
       </c>
       <c r="B12" t="n">
-        <v>57953</v>
+        <v>83305</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6486</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Öretjärnbäcken, Dlr</t>
+          <t>Kerstibygget, Kerstibygget, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>362415</v>
+        <v>363129</v>
       </c>
       <c r="R12" t="n">
-        <v>6883113</v>
+        <v>6882975</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1959,17 +1955,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-08-25</t>
+          <t>2025-01-04</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-08-25</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>savhack</t>
+          <t>2025-01-04</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1984,24 +1985,24 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Carl Wiking</t>
+          <t>Andreas Öster</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Carl Wiking</t>
+          <t>Andreas Öster, Maria Hindemo, Cecilia Öster</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119352008</t>
+          <t>https://artportalen.se/Sighting/121898927</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120683552</v>
+        <v>82113833</v>
       </c>
       <c r="B13" t="n">
         <v>57953</v>
@@ -2029,32 +2030,28 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Västerkölen, Dlr</t>
+          <t>Grövelsjön, Lövåsen, drygt 1 km VNV Lövåsen utefter skidspåret, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>362763</v>
+        <v>362381</v>
       </c>
       <c r="R13" t="n">
-        <v>6883151</v>
+        <v>6883040</v>
       </c>
       <c r="S13" t="n">
-        <v>4</v>
+        <v>100</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2078,22 +2075,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>15:18</t>
+          <t>2020-02-09</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>15:18</t>
+          <t>2020-02-09</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Hackspår på tall o gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2104,28 +2096,38 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Fjällblandskog</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Äldre fjällnära skog; mycket småmyrar</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Mats Lindqvist</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Mats Lindqvist</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120683552</t>
+          <t>https://artportalen.se/Sighting/82113833</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121206319</v>
+        <v>114387742</v>
       </c>
       <c r="B14" t="n">
         <v>57953</v>
@@ -2153,20 +2155,32 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Kerstibygget, Kerstibygget, Dlr</t>
+          <t>Kokällmyren, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>363246</v>
+        <v>362387</v>
       </c>
       <c r="R14" t="n">
-        <v>6883004</v>
+        <v>6883024</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2190,22 +2204,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-01-25</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-01-25</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2220,24 +2234,24 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121206319</t>
+          <t>https://artportalen.se/Sighting/114387742</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128821311</v>
+        <v>119352008</v>
       </c>
       <c r="B15" t="n">
         <v>57953</v>
@@ -2265,32 +2279,24 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Kokällmyren, Dlr</t>
+          <t>Öretjärnbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>362158</v>
+        <v>362415</v>
       </c>
       <c r="R15" t="n">
-        <v>6882996</v>
+        <v>6883113</v>
       </c>
       <c r="S15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2314,22 +2320,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>11:43</t>
+          <t>2024-08-25</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>11:43</t>
+          <t>2024-08-25</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>savhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2344,27 +2345,27 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Carl Wiking</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Carl Wiking</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128821311</t>
+          <t>https://artportalen.se/Sighting/119352008</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119871769</v>
+        <v>120683552</v>
       </c>
       <c r="B16" t="n">
-        <v>58057</v>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2372,16 +2373,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2391,32 +2392,30 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Kokällmyren, Kokällmyren, Dlr</t>
+          <t>Västerkölen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>361903</v>
+        <v>362763</v>
       </c>
       <c r="R16" t="n">
-        <v>6883079</v>
+        <v>6883151</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2440,22 +2439,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2470,69 +2469,65 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>John-Olof Halvarsson</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>John-Olof Halvarsson</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119871769</t>
+          <t>https://artportalen.se/Sighting/120683552</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127172331</v>
+        <v>121206319</v>
       </c>
       <c r="B17" t="n">
-        <v>97983</v>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Kerstibygget, Dlr</t>
+          <t>Kerstibygget, Kerstibygget, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>363170</v>
+        <v>363246</v>
       </c>
       <c r="R17" t="n">
-        <v>6882973</v>
+        <v>6883004</v>
       </c>
       <c r="S17" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2556,22 +2551,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2586,70 +2581,74 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127172331</t>
+          <t>https://artportalen.se/Sighting/121206319</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128820996</v>
+        <v>128821311</v>
       </c>
       <c r="B18" t="n">
-        <v>97983</v>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Kokällmyren, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>361948</v>
+        <v>362158</v>
       </c>
       <c r="R18" t="n">
-        <v>6883107</v>
+        <v>6882996</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
@@ -2681,7 +2680,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2691,7 +2690,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2717,74 +2716,68 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128820996</t>
+          <t>https://artportalen.se/Sighting/128821311</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>79128510</v>
+        <v>119871769</v>
       </c>
       <c r="B19" t="n">
-        <v>99140</v>
+        <v>58057</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221952</v>
+        <v>103031</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr"/>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>stationär</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Lövåsens fjällgård 1360 m VNV, Dlr</t>
+          <t>Kokällmyren, Kokällmyren, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>362267</v>
+        <v>361903</v>
       </c>
       <c r="R19" t="n">
-        <v>6883057</v>
+        <v>6883079</v>
       </c>
       <c r="S19" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2808,12 +2801,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2019-07-20</t>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2019-07-20</t>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2822,23 +2825,381 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Ole Tryggeson</t>
+          <t>John-Olof Halvarsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Ole Tryggeson</t>
+          <t>John-Olof Halvarsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119871769</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>127172331</v>
+      </c>
+      <c r="B20" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Kerstibygget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>363170</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6882973</v>
+      </c>
+      <c r="S20" t="n">
+        <v>4</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Idre</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127172331</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>128820996</v>
+      </c>
+      <c r="B21" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Kokällmyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>361948</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6883107</v>
+      </c>
+      <c r="S21" t="n">
+        <v>4</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Idre</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>11:29</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>11:29</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Michael Lander</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128820996</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>79128510</v>
+      </c>
+      <c r="B22" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Lövåsens fjällgård 1360 m VNV, Dlr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>362267</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6883057</v>
+      </c>
+      <c r="S22" t="n">
+        <v>50</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Idre</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2019-07-20</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2019-07-20</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Ole Tryggeson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Ole Tryggeson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/79128510</t>
         </is>
@@ -2864,6 +3225,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 33882-2024 artfynd.xlsx
+++ b/artfynd/A 33882-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136872860</v>
       </c>
       <c r="B2" t="n">
-        <v>79555</v>
+        <v>79559</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
         <v>136872944</v>
       </c>
       <c r="B6" t="n">
-        <v>92035</v>
+        <v>92037</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1770,7 +1770,7 @@
         <v>136873109</v>
       </c>
       <c r="B11" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 33882-2024 artfynd.xlsx
+++ b/artfynd/A 33882-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136872860</v>
       </c>
       <c r="B2" t="n">
-        <v>79559</v>
+        <v>79561</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
         <v>136872944</v>
       </c>
       <c r="B6" t="n">
-        <v>92037</v>
+        <v>92039</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1770,7 +1770,7 @@
         <v>136873109</v>
       </c>
       <c r="B11" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 33882-2024 artfynd.xlsx
+++ b/artfynd/A 33882-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ22"/>
+  <dimension ref="A1:AZ23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1281,55 +1281,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>114387775</v>
+        <v>137077815</v>
       </c>
       <c r="B7" t="n">
-        <v>79327</v>
+        <v>92080</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kokällmyren, Dlr</t>
+          <t>Kerstibygget, Sågliden SV Grövelsjön, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>362379</v>
+        <v>362887</v>
       </c>
       <c r="R7" t="n">
-        <v>6883037</v>
+        <v>6883106</v>
       </c>
       <c r="S7" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1353,27 +1346,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-01-25</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-01-25</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:33</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Granar draperade med garnlav</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1388,24 +1376,24 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/114387775</t>
+          <t>https://artportalen.se/Sighting/137077815</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120682160</v>
+        <v>114387775</v>
       </c>
       <c r="B8" t="n">
         <v>79327</v>
@@ -1434,26 +1422,26 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Västerkölen, Dlr</t>
+          <t>Kokällmyren, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>362634</v>
+        <v>362379</v>
       </c>
       <c r="R8" t="n">
-        <v>6882998</v>
+        <v>6883037</v>
       </c>
       <c r="S8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1477,27 +1465,27 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-01-25</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-01-25</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Draperade granar i naturskog. Garnlav med apothecier</t>
+          <t>Granar draperade med garnlav</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1523,13 +1511,13 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120682160</t>
+          <t>https://artportalen.se/Sighting/114387775</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128821017</v>
+        <v>120682160</v>
       </c>
       <c r="B9" t="n">
         <v>79327</v>
@@ -1558,26 +1546,26 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kokällmyren, Dlr</t>
+          <t>Västerkölen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>361967</v>
+        <v>362634</v>
       </c>
       <c r="R9" t="n">
-        <v>6883096</v>
+        <v>6882998</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1601,22 +1589,27 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Draperade granar i naturskog. Garnlav med apothecier</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1642,13 +1635,13 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128821017</t>
+          <t>https://artportalen.se/Sighting/120682160</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128821031</v>
+        <v>128821017</v>
       </c>
       <c r="B10" t="n">
         <v>79327</v>
@@ -1690,13 +1683,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>361972</v>
+        <v>361967</v>
       </c>
       <c r="R10" t="n">
-        <v>6883098</v>
+        <v>6883096</v>
       </c>
       <c r="S10" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1725,7 +1718,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1735,7 +1728,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1761,16 +1754,16 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128821031</t>
+          <t>https://artportalen.se/Sighting/128821017</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>136873109</v>
+        <v>128821031</v>
       </c>
       <c r="B11" t="n">
-        <v>79482</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1801,25 +1794,21 @@
           <t>bålar</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Kerstibygget, Dlr</t>
+          <t>Kokällmyren, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>363276</v>
+        <v>361972</v>
       </c>
       <c r="R11" t="n">
-        <v>6883022</v>
+        <v>6883098</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1843,22 +1832,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1884,16 +1873,16 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136873109</t>
+          <t>https://artportalen.se/Sighting/128821031</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121898927</v>
+        <v>136873109</v>
       </c>
       <c r="B12" t="n">
-        <v>83305</v>
+        <v>79482</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1901,37 +1890,48 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6486</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Kerstibygget, Kerstibygget, Dlr</t>
+          <t>Kerstibygget, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>363129</v>
+        <v>363276</v>
       </c>
       <c r="R12" t="n">
-        <v>6882975</v>
+        <v>6883022</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1955,22 +1955,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-01-04</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-01-04</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1985,73 +1985,65 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Andreas Öster, Maria Hindemo, Cecilia Öster</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121898927</t>
+          <t>https://artportalen.se/Sighting/136873109</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>82113833</v>
+        <v>121898927</v>
       </c>
       <c r="B13" t="n">
-        <v>57953</v>
+        <v>83305</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6486</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Grövelsjön, Lövåsen, drygt 1 km VNV Lövåsen utefter skidspåret, Dlr</t>
+          <t>Kerstibygget, Kerstibygget, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>362381</v>
+        <v>363129</v>
       </c>
       <c r="R13" t="n">
-        <v>6883040</v>
+        <v>6882975</v>
       </c>
       <c r="S13" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2075,17 +2067,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2020-02-09</t>
+          <t>2025-01-04</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2020-02-09</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Hackspår på tall o gran</t>
+          <t>2025-01-04</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2096,38 +2093,28 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>Fjällblandskog</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>Äldre fjällnära skog; mycket småmyrar</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Mats Lindqvist</t>
+          <t>Andreas Öster</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Mats Lindqvist</t>
+          <t>Andreas Öster, Maria Hindemo, Cecilia Öster</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/82113833</t>
+          <t>https://artportalen.se/Sighting/121898927</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>114387742</v>
+        <v>82113833</v>
       </c>
       <c r="B14" t="n">
         <v>57953</v>
@@ -2155,32 +2142,28 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Kokällmyren, Dlr</t>
+          <t>Grövelsjön, Lövåsen, drygt 1 km VNV Lövåsen utefter skidspåret, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>362387</v>
+        <v>362381</v>
       </c>
       <c r="R14" t="n">
-        <v>6883024</v>
+        <v>6883040</v>
       </c>
       <c r="S14" t="n">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2204,22 +2187,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-01-25</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>15:31</t>
+          <t>2020-02-09</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-01-25</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>15:31</t>
+          <t>2020-02-09</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Hackspår på tall o gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2230,28 +2208,38 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Fjällblandskog</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Äldre fjällnära skog; mycket småmyrar</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Mats Lindqvist</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Mats Lindqvist</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/114387742</t>
+          <t>https://artportalen.se/Sighting/82113833</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119352008</v>
+        <v>114387742</v>
       </c>
       <c r="B15" t="n">
         <v>57953</v>
@@ -2279,24 +2267,32 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Öretjärnbäcken, Dlr</t>
+          <t>Kokällmyren, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>362415</v>
+        <v>362387</v>
       </c>
       <c r="R15" t="n">
-        <v>6883113</v>
+        <v>6883024</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2320,17 +2316,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-08-25</t>
+          <t>2024-01-25</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-08-25</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>savhack</t>
+          <t>2024-01-25</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2345,24 +2346,24 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Carl Wiking</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Carl Wiking</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119352008</t>
+          <t>https://artportalen.se/Sighting/114387742</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120683552</v>
+        <v>119352008</v>
       </c>
       <c r="B16" t="n">
         <v>57953</v>
@@ -2390,32 +2391,24 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Västerkölen, Dlr</t>
+          <t>Öretjärnbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>362763</v>
+        <v>362415</v>
       </c>
       <c r="R16" t="n">
-        <v>6883151</v>
+        <v>6883113</v>
       </c>
       <c r="S16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2439,22 +2432,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>15:18</t>
+          <t>2024-08-25</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>15:18</t>
+          <t>2024-08-25</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>savhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2469,24 +2457,24 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Carl Wiking</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Carl Wiking</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120683552</t>
+          <t>https://artportalen.se/Sighting/119352008</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121206319</v>
+        <v>120683552</v>
       </c>
       <c r="B17" t="n">
         <v>57953</v>
@@ -2514,20 +2502,32 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Kerstibygget, Kerstibygget, Dlr</t>
+          <t>Västerkölen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>363246</v>
+        <v>362763</v>
       </c>
       <c r="R17" t="n">
-        <v>6883004</v>
+        <v>6883151</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2551,22 +2551,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2581,24 +2581,24 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Maria Hindemo</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121206319</t>
+          <t>https://artportalen.se/Sighting/120683552</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128821311</v>
+        <v>121206319</v>
       </c>
       <c r="B18" t="n">
         <v>57953</v>
@@ -2626,32 +2626,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Kokällmyren, Dlr</t>
+          <t>Kerstibygget, Kerstibygget, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>362158</v>
+        <v>363246</v>
       </c>
       <c r="R18" t="n">
-        <v>6882996</v>
+        <v>6883004</v>
       </c>
       <c r="S18" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2675,22 +2663,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2705,27 +2693,27 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128821311</t>
+          <t>https://artportalen.se/Sighting/121206319</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119871769</v>
+        <v>128821311</v>
       </c>
       <c r="B19" t="n">
-        <v>58057</v>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2733,16 +2721,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2752,32 +2740,30 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Kokällmyren, Kokällmyren, Dlr</t>
+          <t>Kokällmyren, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>361903</v>
+        <v>362158</v>
       </c>
       <c r="R19" t="n">
-        <v>6883079</v>
+        <v>6882996</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2801,22 +2787,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2831,69 +2817,79 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>John-Olof Halvarsson</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>John-Olof Halvarsson</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119871769</t>
+          <t>https://artportalen.se/Sighting/128821311</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127172331</v>
+        <v>119871769</v>
       </c>
       <c r="B20" t="n">
-        <v>97983</v>
+        <v>58057</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221945</v>
+        <v>103031</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Kerstibygget, Dlr</t>
+          <t>Kokällmyren, Kokällmyren, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>363170</v>
+        <v>361903</v>
       </c>
       <c r="R20" t="n">
-        <v>6882973</v>
+        <v>6883079</v>
       </c>
       <c r="S20" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2917,22 +2913,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2947,24 +2943,24 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>John-Olof Halvarsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Michael Lander</t>
+          <t>John-Olof Halvarsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127172331</t>
+          <t>https://artportalen.se/Sighting/119871769</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128820996</v>
+        <v>127172331</v>
       </c>
       <c r="B21" t="n">
         <v>97983</v>
@@ -2996,21 +2992,17 @@
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Kokällmyren, Dlr</t>
+          <t>Kerstibygget, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>361948</v>
+        <v>363170</v>
       </c>
       <c r="R21" t="n">
-        <v>6883107</v>
+        <v>6882973</v>
       </c>
       <c r="S21" t="n">
         <v>4</v>
@@ -3037,22 +3029,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3078,16 +3070,16 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128820996</t>
+          <t>https://artportalen.se/Sighting/127172331</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>79128510</v>
+        <v>128820996</v>
       </c>
       <c r="B22" t="n">
-        <v>99140</v>
+        <v>97983</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3095,38 +3087,26 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221952</v>
+        <v>221945</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr">
         <is>
@@ -3135,17 +3115,17 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Lövåsens fjällgård 1360 m VNV, Dlr</t>
+          <t>Kokällmyren, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>362267</v>
+        <v>361948</v>
       </c>
       <c r="R22" t="n">
-        <v>6883057</v>
+        <v>6883107</v>
       </c>
       <c r="S22" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3169,12 +3149,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2019-07-20</t>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2019-07-20</t>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3183,23 +3173,145 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Ole Tryggeson</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Ole Tryggeson</t>
+          <t>Michael Lander</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128820996</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>79128510</v>
+      </c>
+      <c r="B23" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Lövåsens fjällgård 1360 m VNV, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>362267</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6883057</v>
+      </c>
+      <c r="S23" t="n">
+        <v>50</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Idre</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2019-07-20</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2019-07-20</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Ole Tryggeson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Ole Tryggeson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/79128510</t>
         </is>
@@ -3228,6 +3340,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 33882-2024 artfynd.xlsx
+++ b/artfynd/A 33882-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136872860</v>
       </c>
       <c r="B2" t="n">
-        <v>79561</v>
+        <v>79562</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
         <v>136872944</v>
       </c>
       <c r="B6" t="n">
-        <v>92039</v>
+        <v>92040</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>137077815</v>
       </c>
       <c r="B7" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1882,7 +1882,7 @@
         <v>136873109</v>
       </c>
       <c r="B12" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 33882-2024 artfynd.xlsx
+++ b/artfynd/A 33882-2024 artfynd.xlsx
@@ -1165,7 +1165,7 @@
         <v>136872944</v>
       </c>
       <c r="B6" t="n">
-        <v>92040</v>
+        <v>92046</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>137077815</v>
       </c>
       <c r="B7" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 33882-2024 artfynd.xlsx
+++ b/artfynd/A 33882-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136872860</v>
       </c>
       <c r="B2" t="n">
-        <v>79562</v>
+        <v>79564</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
         <v>136872944</v>
       </c>
       <c r="B6" t="n">
-        <v>92046</v>
+        <v>92050</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>137077815</v>
       </c>
       <c r="B7" t="n">
-        <v>92087</v>
+        <v>92091</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1882,7 +1882,7 @@
         <v>136873109</v>
       </c>
       <c r="B12" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 33882-2024 artfynd.xlsx
+++ b/artfynd/A 33882-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136872860</v>
       </c>
       <c r="B2" t="n">
-        <v>79564</v>
+        <v>79567</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
         <v>136872944</v>
       </c>
       <c r="B6" t="n">
-        <v>92050</v>
+        <v>92052</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>137077815</v>
       </c>
       <c r="B7" t="n">
-        <v>92091</v>
+        <v>92093</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1882,7 +1882,7 @@
         <v>136873109</v>
       </c>
       <c r="B12" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 33882-2024 artfynd.xlsx
+++ b/artfynd/A 33882-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136872860</v>
       </c>
       <c r="B2" t="n">
-        <v>79567</v>
+        <v>79580</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
         <v>136872944</v>
       </c>
       <c r="B6" t="n">
-        <v>92052</v>
+        <v>92065</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>137077815</v>
       </c>
       <c r="B7" t="n">
-        <v>92093</v>
+        <v>92106</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1882,7 +1882,7 @@
         <v>136873109</v>
       </c>
       <c r="B12" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 33882-2024 artfynd.xlsx
+++ b/artfynd/A 33882-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136872860</v>
       </c>
       <c r="B2" t="n">
-        <v>79580</v>
+        <v>79582</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
         <v>136872944</v>
       </c>
       <c r="B6" t="n">
-        <v>92065</v>
+        <v>92067</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>137077815</v>
       </c>
       <c r="B7" t="n">
-        <v>92106</v>
+        <v>92108</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1882,7 +1882,7 @@
         <v>136873109</v>
       </c>
       <c r="B12" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 33882-2024 artfynd.xlsx
+++ b/artfynd/A 33882-2024 artfynd.xlsx
@@ -1913,11 +1913,7 @@
           <t>bålar</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>

--- a/artfynd/A 33882-2024 artfynd.xlsx
+++ b/artfynd/A 33882-2024 artfynd.xlsx
@@ -1165,7 +1165,7 @@
         <v>136872944</v>
       </c>
       <c r="B6" t="n">
-        <v>92067</v>
+        <v>92070</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>137077815</v>
       </c>
       <c r="B7" t="n">
-        <v>92108</v>
+        <v>92111</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 33882-2024 artfynd.xlsx
+++ b/artfynd/A 33882-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136872860</v>
       </c>
       <c r="B2" t="n">
-        <v>79582</v>
+        <v>79592</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
         <v>136872944</v>
       </c>
       <c r="B6" t="n">
-        <v>92070</v>
+        <v>92080</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>137077815</v>
       </c>
       <c r="B7" t="n">
-        <v>92111</v>
+        <v>92121</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1882,7 +1882,7 @@
         <v>136873109</v>
       </c>
       <c r="B12" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 33882-2024 artfynd.xlsx
+++ b/artfynd/A 33882-2024 artfynd.xlsx
@@ -1165,7 +1165,7 @@
         <v>136872944</v>
       </c>
       <c r="B6" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>137077815</v>
       </c>
       <c r="B7" t="n">
-        <v>92121</v>
+        <v>92122</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 33882-2024 artfynd.xlsx
+++ b/artfynd/A 33882-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136872860</v>
       </c>
       <c r="B2" t="n">
-        <v>79592</v>
+        <v>79595</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
         <v>136872944</v>
       </c>
       <c r="B6" t="n">
-        <v>92081</v>
+        <v>92084</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>137077815</v>
       </c>
       <c r="B7" t="n">
-        <v>92122</v>
+        <v>92125</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1882,7 +1882,7 @@
         <v>136873109</v>
       </c>
       <c r="B12" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 33882-2024 artfynd.xlsx
+++ b/artfynd/A 33882-2024 artfynd.xlsx
@@ -1165,7 +1165,7 @@
         <v>136872944</v>
       </c>
       <c r="B6" t="n">
-        <v>92084</v>
+        <v>92086</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>137077815</v>
       </c>
       <c r="B7" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 33882-2024 artfynd.xlsx
+++ b/artfynd/A 33882-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136872860</v>
       </c>
       <c r="B2" t="n">
-        <v>79595</v>
+        <v>79600</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
         <v>136872944</v>
       </c>
       <c r="B6" t="n">
-        <v>92086</v>
+        <v>92091</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>137077815</v>
       </c>
       <c r="B7" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1882,7 +1882,7 @@
         <v>136873109</v>
       </c>
       <c r="B12" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 33882-2024 artfynd.xlsx
+++ b/artfynd/A 33882-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136872860</v>
       </c>
       <c r="B2" t="n">
-        <v>79600</v>
+        <v>79611</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
         <v>136872944</v>
       </c>
       <c r="B6" t="n">
-        <v>92091</v>
+        <v>92103</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>137077815</v>
       </c>
       <c r="B7" t="n">
-        <v>92132</v>
+        <v>92144</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1882,7 +1882,7 @@
         <v>136873109</v>
       </c>
       <c r="B12" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 33882-2024 artfynd.xlsx
+++ b/artfynd/A 33882-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136872860</v>
       </c>
       <c r="B2" t="n">
-        <v>79611</v>
+        <v>79612</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
         <v>136872944</v>
       </c>
       <c r="B6" t="n">
-        <v>92103</v>
+        <v>92104</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         <v>137077815</v>
       </c>
       <c r="B7" t="n">
-        <v>92144</v>
+        <v>92145</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1882,7 +1882,7 @@
         <v>136873109</v>
       </c>
       <c r="B12" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 33882-2024 artfynd.xlsx
+++ b/artfynd/A 33882-2024 artfynd.xlsx
@@ -1284,7 +1284,7 @@
         <v>137077815</v>
       </c>
       <c r="B7" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 33882-2024 artfynd.xlsx
+++ b/artfynd/A 33882-2024 artfynd.xlsx
@@ -1284,7 +1284,7 @@
         <v>137077815</v>
       </c>
       <c r="B7" t="n">
-        <v>92148</v>
+        <v>92152</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
